--- a/ThreadsGrid.xlsx
+++ b/ThreadsGrid.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TWÖRK\CODE\RemoveBackground\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TOOLS\RemoveBackground\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A880F1B4-FAC4-46FD-AB41-5E410A610D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09178424-C443-4FFF-9976-2D547A4B764F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Connect-8" sheetId="2" r:id="rId1"/>
-    <sheet name="Connect-4" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="Connect-4" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -90,7 +91,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -473,6 +474,19 @@
     <border>
       <left/>
       <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -487,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -555,9 +569,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -579,10 +590,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -609,16 +620,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -632,7 +633,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
@@ -641,12 +642,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -924,74 +937,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E43AE5-322C-48A4-B0A0-321A33E89217}">
-  <dimension ref="B1:S24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:R24"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="9" max="9" width="10.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="K1" s="23" t="s">
+    <row r="1" spans="2:18" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="M1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-    </row>
-    <row r="2" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="9">
         <v>0</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
-      <c r="F2" s="26"/>
+      <c r="F2" s="25"/>
       <c r="G2" s="17"/>
       <c r="H2" s="11">
         <v>2</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="49" t="s">
+      <c r="L2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="50" t="s">
+      <c r="M2" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="52">
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="47">
         <v>2</v>
       </c>
-      <c r="S2" s="44"/>
-    </row>
-    <row r="3" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="12"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="6"/>
       <c r="G3" s="5"/>
       <c r="H3" s="13"/>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="53" t="s">
+      <c r="L3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="42" t="s">
+      <c r="M3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N3" s="3"/>
@@ -999,99 +1005,81 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="19"/>
-      <c r="S3" s="44"/>
-    </row>
-    <row r="4" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="12"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
       <c r="H4" s="13"/>
-      <c r="K4" s="44"/>
       <c r="L4" s="12"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
       <c r="R4" s="13"/>
-      <c r="S4" s="44"/>
-    </row>
-    <row r="5" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="25"/>
+    </row>
+    <row r="5" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="24"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="23" t="s">
         <v>1</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="H5" s="13"/>
-      <c r="K5" s="44"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
       <c r="R5" s="13"/>
-      <c r="S5" s="44"/>
-    </row>
-    <row r="6" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="12"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
       <c r="E6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="H6" s="18"/>
-      <c r="K6" s="44"/>
       <c r="L6" s="12"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
       <c r="R6" s="13"/>
-      <c r="S6" s="44"/>
-    </row>
-    <row r="7" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="12"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
       <c r="E7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="42" t="s">
+      <c r="G7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H7" s="19"/>
-      <c r="K7" s="44"/>
       <c r="L7" s="12"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
       <c r="R7" s="13"/>
-      <c r="S7" s="44"/>
-    </row>
-    <row r="8" spans="2:19" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="2:18" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="14">
         <v>1</v>
       </c>
@@ -1103,7 +1091,6 @@
       <c r="H8" s="16">
         <v>3</v>
       </c>
-      <c r="K8" s="44"/>
       <c r="L8" s="14"/>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
@@ -1113,11 +1100,10 @@
       <c r="R8" s="16">
         <v>3</v>
       </c>
-      <c r="S8" s="44"/>
-    </row>
-    <row r="9" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="10" spans="2:19" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="2:18" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="11" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="9">
         <v>0</v>
       </c>
@@ -1127,95 +1113,79 @@
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="11"/>
-      <c r="I11" s="44"/>
-    </row>
-    <row r="12" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="12"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
       <c r="H12" s="13"/>
-      <c r="I12" s="44"/>
-    </row>
-    <row r="13" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="12"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
       <c r="H13" s="13"/>
-      <c r="I13" s="44"/>
-    </row>
-    <row r="14" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="12"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
       <c r="H14" s="13"/>
-      <c r="I14" s="44"/>
-    </row>
-    <row r="15" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="12"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
       <c r="H15" s="13"/>
-      <c r="I15" s="44"/>
-    </row>
-    <row r="16" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="25"/>
+    </row>
+    <row r="16" spans="2:18" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="24"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
       <c r="G16" s="8" t="s">
         <v>2</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="I16" s="23" t="s">
+      <c r="I16" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="46">
+      <c r="B17" s="41">
         <v>1</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="48" t="s">
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="40" t="s">
+      <c r="H17" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="I17" s="41" t="s">
+      <c r="I17" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="23" t="s">
+      <c r="G18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H18" s="41" t="s">
+      <c r="H18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I18" s="41" t="s">
+      <c r="I18" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1231,9 +1201,136 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{428737F7-295F-4084-8C65-C765F84E4796}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="10" width="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="48"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="50"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="60"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="53"/>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="59"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="56"/>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B6" s="48">
+        <v>71</v>
+      </c>
+      <c r="C6" s="49">
+        <v>61</v>
+      </c>
+      <c r="D6" s="49">
+        <v>51</v>
+      </c>
+      <c r="E6" s="49">
+        <v>52</v>
+      </c>
+      <c r="F6" s="49">
+        <v>53</v>
+      </c>
+      <c r="G6" s="50"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B7" s="51">
+        <v>81</v>
+      </c>
+      <c r="C7" s="52">
+        <v>7</v>
+      </c>
+      <c r="D7" s="52">
+        <v>6</v>
+      </c>
+      <c r="E7" s="52">
+        <v>5</v>
+      </c>
+      <c r="F7" s="62">
+        <v>44</v>
+      </c>
+      <c r="G7" s="53"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B8" s="51">
+        <v>15</v>
+      </c>
+      <c r="C8" s="52">
+        <v>8</v>
+      </c>
+      <c r="D8" s="52">
+        <v>0</v>
+      </c>
+      <c r="E8" s="52">
+        <v>4</v>
+      </c>
+      <c r="F8" s="62">
+        <v>33</v>
+      </c>
+      <c r="G8" s="53"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B9" s="51">
+        <v>14</v>
+      </c>
+      <c r="C9" s="52">
+        <v>1</v>
+      </c>
+      <c r="D9" s="52">
+        <v>2</v>
+      </c>
+      <c r="E9" s="52">
+        <v>3</v>
+      </c>
+      <c r="F9" s="62">
+        <v>32</v>
+      </c>
+      <c r="G9" s="53"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B10" s="51">
+        <v>11</v>
+      </c>
+      <c r="C10" s="62">
+        <v>12</v>
+      </c>
+      <c r="D10" s="62">
+        <v>13</v>
+      </c>
+      <c r="E10" s="62">
+        <v>21</v>
+      </c>
+      <c r="F10" s="62">
+        <v>31</v>
+      </c>
+      <c r="G10" s="53"/>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="54"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="56"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:S36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="16" width="10.90625" style="1" customWidth="1"/>
     <col min="17" max="16384" width="8.7265625" style="1"/>
@@ -1261,47 +1358,26 @@
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
       <c r="R2" s="11"/>
-      <c r="S2" s="23"/>
     </row>
     <row r="3" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="5"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
       <c r="F3" s="6"/>
       <c r="G3" s="5"/>
       <c r="H3" s="6"/>
       <c r="L3" s="12"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23"/>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
       <c r="R3" s="13"/>
-      <c r="S3" s="23"/>
     </row>
     <row r="4" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
       <c r="F4" s="6"/>
       <c r="G4" s="5"/>
       <c r="H4" s="6"/>
       <c r="L4" s="12"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
       <c r="R4" s="13"/>
-      <c r="S4" s="23"/>
     </row>
     <row r="5" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="5"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="6" t="s">
@@ -1312,13 +1388,7 @@
       </c>
       <c r="H5" s="6"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
       <c r="R5" s="13"/>
-      <c r="S5" s="23"/>
     </row>
     <row r="6" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="7"/>
@@ -1327,21 +1397,15 @@
       <c r="E6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="24"/>
+      <c r="H6" s="23"/>
       <c r="L6" s="12"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
       <c r="R6" s="13"/>
-      <c r="S6" s="23"/>
     </row>
     <row r="7" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="2"/>
@@ -1350,25 +1414,21 @@
       <c r="E7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="28" t="s">
         <v>6</v>
       </c>
       <c r="H7" s="4"/>
       <c r="L7" s="12"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23" t="s">
+      <c r="Q7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="R7" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="S7" s="23" t="s">
+      <c r="S7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1379,9 +1439,9 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
-      <c r="F8" s="24"/>
+      <c r="F8" s="23"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="24">
+      <c r="H8" s="23">
         <v>4</v>
       </c>
       <c r="L8" s="14"/>
@@ -1392,39 +1452,27 @@
       <c r="Q8" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="40" t="s">
+      <c r="R8" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="S8" s="32" t="s">
+      <c r="S8" s="31" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23" t="s">
+      <c r="Q9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="R9" s="32" t="s">
+      <c r="R9" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="S9" s="32" t="s">
+      <c r="S9" s="31" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="32"/>
-      <c r="S10" s="32"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
     </row>
     <row r="11" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="9">
@@ -1436,10 +1484,7 @@
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="11"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="35">
+      <c r="L11" s="34">
         <v>1</v>
       </c>
       <c r="M11" s="17"/>
@@ -1453,37 +1498,28 @@
     </row>
     <row r="12" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="12"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23" t="s">
+      <c r="G12" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="36" t="s">
+      <c r="L12" s="35" t="s">
         <v>1</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
       <c r="R12" s="13"/>
     </row>
     <row r="13" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="25"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -1491,20 +1527,20 @@
       <c r="G13" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="H13" s="33" t="s">
+      <c r="H13" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="32"/>
-      <c r="K13" s="23" t="s">
+      <c r="J13" s="31"/>
+      <c r="K13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L13" s="37" t="s">
+      <c r="L13" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="M13" s="28" t="s">
+      <c r="M13" s="27" t="s">
         <v>8</v>
       </c>
       <c r="N13" s="8"/>
@@ -1522,20 +1558,20 @@
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="34" t="s">
+      <c r="H14" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="32" t="s">
+      <c r="I14" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="J14" s="32"/>
-      <c r="K14" s="23" t="s">
+      <c r="J14" s="31"/>
+      <c r="K14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="38" t="s">
+      <c r="L14" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="29" t="s">
+      <c r="M14" s="28" t="s">
         <v>6</v>
       </c>
       <c r="N14" s="3"/>
@@ -1546,40 +1582,16 @@
     </row>
     <row r="15" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="12"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
       <c r="H15" s="13"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="36"/>
+      <c r="L15" s="35"/>
       <c r="M15" s="5"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
       <c r="R15" s="13"/>
     </row>
     <row r="16" spans="2:19" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="12"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
       <c r="H16" s="13"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="36"/>
+      <c r="L16" s="35"/>
       <c r="M16" s="5"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
       <c r="R16" s="13"/>
     </row>
     <row r="17" spans="2:18" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1592,10 +1604,7 @@
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
       <c r="H17" s="16"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="39">
+      <c r="L17" s="38">
         <v>2</v>
       </c>
       <c r="M17" s="22"/>
